--- a/Compititor's_Price/Powerlon_Prices/Powerlon_Prices_11-09-2026.xlsx
+++ b/Compititor's_Price/Powerlon_Prices/Powerlon_Prices_11-09-2026.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_lite_92gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8995b890&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_lite_92gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d8860c10&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_standard_115gsm_breather_membrane_1.0m_x_25m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8a35f190&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_standard_115gsm_breather_membrane_1.0m_x_25m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d9250b90&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_standard_115gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8a51ec50&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_standard_115gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d8894910&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_standard_115gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e89f5c390&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_standard_115gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d8e4dd10&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_premium_135gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8a3a7cd0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_premium_135gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d927f010&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_premium_135gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8ad607d0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_premium_135gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d9a5edd0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_max_155gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8a1d82d0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_max_155gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d88e5510&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_max_155gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8af0ee50&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_max_155gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d8a0d1d0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_supaperm_sp100_housewrap_1.6m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e89c79810&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_supaperm_sp100_housewrap_1.6m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d977cd90&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -859,30 +859,30 @@
       <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: invalid argument
-  (Session info: chrome=152.0.7977.83)
+  (Session info: chrome=153.0.8010.37)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff62083e035+5745]
-	chromedriver!(No symbol) [0x7ff620766a90]
-	chromedriver!(No symbol) [0x7ff620595b66]
-	chromedriver!(No symbol) [0x7ff620582458]
-	chromedriver!(No symbol) [0x7ff62058088b]
-	chromedriver!(No symbol) [0x7ff620580e12]
-	chromedriver!(No symbol) [0x7ff620599fd6]
-	chromedriver!(No symbol) [0x7ff62063f314]
-	chromedriver!(No symbol) [0x7ff6206195ca]
-	chromedriver!(No symbol) [0x7ff62063e502]
-	chromedriver!(No symbol) [0x7ff6205e2e4b]
-	chromedriver!(No symbol) [0x7ff6205e3d83]
-	chromedriver!GetHandleVerifier [0x7ff620c52f8b+41a69b]
-	chromedriver!GetHandleVerifier [0x7ff620c80132+447842]
-	chromedriver!GetHandleVerifier [0x7ff620c73e7e+43b58e]
-	chromedriver!GetHandleVerifier [0x7ff620933f5e+fb66e]
-	chromedriver!(No symbol) [0x7ff62077419c]
-	chromedriver!(No symbol) [0x7ff62076fdd4]
-	chromedriver!(No symbol) [0x7ff62076ff64]
-	chromedriver!(No symbol) [0x7ff62075a91c]
-	KERNEL32!BaseThreadInitThunk [0x7ffe2d13cd87+17]
-	ntdll!RtlUserThreadStart [0x7ffe2ef0caec+2c]
+	chromedriver!GetHandleVerifier [0x7ff65ceeff25+5ae5]
+	chromedriver!(No symbol) [0x7ff65ce12210]
+	chromedriver!(No symbol) [0x7ff65cc34896]
+	chromedriver!(No symbol) [0x7ff65cc2113d]
+	chromedriver!(No symbol) [0x7ff65cc1f694]
+	chromedriver!(No symbol) [0x7ff65cc1fc12]
+	chromedriver!(No symbol) [0x7ff65cc38d87]
+	chromedriver!(No symbol) [0x7ff65cce0ea4]
+	chromedriver!(No symbol) [0x7ff65ccb98fa]
+	chromedriver!(No symbol) [0x7ff65cce00df]
+	chromedriver!(No symbol) [0x7ff65cc82202]
+	chromedriver!(No symbol) [0x7ff65cc83013]
+	chromedriver!GetHandleVerifier [0x7ff65d314231+429df1]
+	chromedriver!GetHandleVerifier [0x7ff65d33fce7+4558a7]
+	chromedriver!GetHandleVerifier [0x7ff65d33413e+449cfe]
+	chromedriver!GetHandleVerifier [0x7ff65cfec9ce+10258e]
+	chromedriver!(No symbol) [0x7ff65ce20545]
+	chromedriver!(No symbol) [0x7ff65ce1b6a4]
+	chromedriver!(No symbol) [0x7ff65ce1b834]
+	chromedriver!(No symbol) [0x7ff65ce0601c]
+	KERNEL32!BaseThreadInitThunk [0x7ffc6d6fcd87+17]
+	ntdll!RtlUserThreadStart [0x7ffc6f34caec+2c]
 </t>
         </is>
       </c>
@@ -893,7 +893,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_supaperm_sp100_housewrap_2.7m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e89f97290&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_supaperm_sp100_housewrap_2.7m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d8de23d0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_vcl_250_vapour_control_layer_2m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8a0d2910&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_vcl_250_vapour_control_layer_2m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d9431890&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultrablock_200_thermo_reflective_vapour_control_layer_1.6m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8a528f90&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultrablock_200_thermo_reflective_vapour_control_layer_1.6m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d91bb010&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_air_barrier_membrane_1.5m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8ae030d0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_air_barrier_membrane_1.5m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d9742b90&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_vcl_170_vapour_control_layer_2m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8aa7b490&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_vcl_170_vapour_control_layer_2m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d9b6b310&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_uv160sa_uv_resistant_facade_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8b02edd0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_uv160sa_uv_resistant_facade_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183da5292d0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_uv120_uv_resistant_facade_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8aae3890&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_uv120_uv_resistant_facade_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d9402c90&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_uv_facade_tape_60mm_x_25m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e89a50150&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_uv_facade_tape_60mm_x_25m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d935af90&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerbond_aluminium_fr_vcl_tape_50mm_x_47.5m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8a15cad0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerbond_aluminium_fr_vcl_tape_50mm_x_47.5m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d9ab7350&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerbond_double_sided_butyl_tape_2mm_x_15mm_x_24m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8aa7a910&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerbond_double_sided_butyl_tape_2mm_x_15mm_x_24m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d86aa790&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_lite_92gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8b67cdd0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_lite_92gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d96fd0d0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_metalix_metal_roof_separation_layer_1.5m_x_25m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8b715b50&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_metalix_metal_roof_separation_layer_1.5m_x_25m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183da081a90&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_supaperm_sp100_housewrap_3.2m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e89f957d0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_supaperm_sp100_housewrap_3.2m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d977ced0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_thermaperm_housewrap_1.5m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8a47bd10&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_thermaperm_housewrap_1.5m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d8e63f50&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_thermaperm_housewrap_2.7m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e89f97690&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_thermaperm_housewrap_2.7m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d977d810&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1809,30 +1809,30 @@
       <c r="E37" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: invalid argument
-  (Session info: chrome=152.0.7977.83)
+  (Session info: chrome=153.0.8010.37)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff68a48e035+5745]
-	chromedriver!(No symbol) [0x7ff68a3b6a90]
-	chromedriver!(No symbol) [0x7ff68a1e5b66]
-	chromedriver!(No symbol) [0x7ff68a1d2458]
-	chromedriver!(No symbol) [0x7ff68a1d088b]
-	chromedriver!(No symbol) [0x7ff68a1d0e12]
-	chromedriver!(No symbol) [0x7ff68a1e9fd6]
-	chromedriver!(No symbol) [0x7ff68a28f314]
-	chromedriver!(No symbol) [0x7ff68a2695ca]
-	chromedriver!(No symbol) [0x7ff68a28e502]
-	chromedriver!(No symbol) [0x7ff68a232e4b]
-	chromedriver!(No symbol) [0x7ff68a233d83]
-	chromedriver!GetHandleVerifier [0x7ff68a8a2f8b+41a69b]
-	chromedriver!GetHandleVerifier [0x7ff68a8d0132+447842]
-	chromedriver!GetHandleVerifier [0x7ff68a8c3e7e+43b58e]
-	chromedriver!GetHandleVerifier [0x7ff68a583f5e+fb66e]
-	chromedriver!(No symbol) [0x7ff68a3c419c]
-	chromedriver!(No symbol) [0x7ff68a3bfdd4]
-	chromedriver!(No symbol) [0x7ff68a3bff64]
-	chromedriver!(No symbol) [0x7ff68a3aa91c]
-	KERNEL32!BaseThreadInitThunk [0x7ffe2d13cd87+17]
-	ntdll!RtlUserThreadStart [0x7ffe2ef0caec+2c]
+	chromedriver!GetHandleVerifier [0x7ff65ceeff25+5ae5]
+	chromedriver!(No symbol) [0x7ff65ce12210]
+	chromedriver!(No symbol) [0x7ff65cc34896]
+	chromedriver!(No symbol) [0x7ff65cc2113d]
+	chromedriver!(No symbol) [0x7ff65cc1f694]
+	chromedriver!(No symbol) [0x7ff65cc1fc12]
+	chromedriver!(No symbol) [0x7ff65cc38d87]
+	chromedriver!(No symbol) [0x7ff65cce0ea4]
+	chromedriver!(No symbol) [0x7ff65ccb98fa]
+	chromedriver!(No symbol) [0x7ff65cce00df]
+	chromedriver!(No symbol) [0x7ff65cc82202]
+	chromedriver!(No symbol) [0x7ff65cc83013]
+	chromedriver!GetHandleVerifier [0x7ff65d314231+429df1]
+	chromedriver!GetHandleVerifier [0x7ff65d33fce7+4558a7]
+	chromedriver!GetHandleVerifier [0x7ff65d33413e+449cfe]
+	chromedriver!GetHandleVerifier [0x7ff65cfec9ce+10258e]
+	chromedriver!(No symbol) [0x7ff65ce20545]
+	chromedriver!(No symbol) [0x7ff65ce1b6a4]
+	chromedriver!(No symbol) [0x7ff65ce1b834]
+	chromedriver!(No symbol) [0x7ff65ce0601c]
+	KERNEL32!BaseThreadInitThunk [0x7ffc6d6fcd87+17]
+	ntdll!RtlUserThreadStart [0x7ffc6f34caec+2c]
 </t>
         </is>
       </c>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultrablock_300_thermo_reflective_vapour_control_layer_2m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e89979ed0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultrablock_300_thermo_reflective_vapour_control_layer_2m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d8d6a690&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_breathe_fire_retardant_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e899b8a10&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_breathe_fire_retardant_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183da254910&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_breathe_fire_retardant_membrane_3m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e89aa3410&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_breathe_fire_retardant_membrane_3m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d8e11910&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/flameout-membrane-sealing-tape-60mm-x-25m (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1016)')))</t>
+          <t>£13.87</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_block_fire_retardant_membrane_2m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8b2d4390&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_block_fire_retardant_membrane_2m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183d8871f10&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_block_plus_fire_retardant_membrane_2m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8ae67c50&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_block_plus_fire_retardant_membrane_2m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183da132850&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_block_class_a_fire_retardant_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x25e8ae70850&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_block_class_a_fire_retardant_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x183da181750&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
         </is>
       </c>
     </row>
